--- a/docs/Matriz_Trazabilidad_HU_RF_Codigo.xlsx
+++ b/docs/Matriz_Trazabilidad_HU_RF_Codigo.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TrazaDoc — MVP de verificación de integridad y trazabilidad documental (Hyperledger Fabric)</t>
+          <t>TrazaDoc: MVP de verificación de integridad y trazabilidad documental (Hyperledger Fabric)</t>
         </is>
       </c>
     </row>
@@ -554,14 +554,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Historias de usuario: 24 — Implementadas 22 · Parciales 1 · No implementadas 1</t>
+          <t>Historias de usuario: 24, Implementadas 22 · Parciales 1 · No implementadas 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Requisitos funcionales: 55 — Implementados 53 · Parciales 1 · No implementados 1  (96 % implementado)</t>
+          <t>Requisitos funcionales: 55, Implementados 53 · Parciales 1 · No implementados 1  (96 % implementado)</t>
         </is>
       </c>
     </row>
@@ -592,14 +592,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1. HU ↔ RF ↔ código — una fila por historia (24).</t>
+          <t>1. HU ↔ RF ↔ código: una fila por historia (24).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2. RF ↔ implementación — una fila por requisito funcional (55).</t>
+          <t>2. RF ↔ implementación: una fila por requisito funcional (55).</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Implementado (con cambio: el rol se toma de la cuenta, no se elige — RF-01)</t>
+          <t>Implementado (con cambio: el rol se toma de la cuenta, no se elige, RF-01)</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Implementado (RNF-10 y RNF-14 sin medición formal todavía — Fase 4)</t>
+          <t>Implementado (RNF-10 y RNF-14 sin medición formal todavía, Fase 4)</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -2336,37 +2336,37 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">

--- a/docs/Matriz_Trazabilidad_HU_RF_Codigo.xlsx
+++ b/docs/Matriz_Trazabilidad_HU_RF_Codigo.xlsx
@@ -50,7 +50,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,16 +70,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -131,12 +121,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -554,14 +538,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Historias de usuario: 24, Implementadas 22 · Parciales 1 · No implementadas 1</t>
+          <t>Historias de usuario: 24, Implementadas 24 · Parciales 0 · No implementadas 0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Requisitos funcionales: 55, Implementados 53 · Parciales 1 · No implementados 1  (96 % implementado)</t>
+          <t>Requisitos funcionales: 55, Implementados 55 · Parciales 0 · No implementados 0  (100 % implementado)</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2258,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>authService.login (failedLoginAttempts, lockedUntil), requireAuth (lastSeenAt)</t>
+          <t>authService.login (failedLoginAttempts, lockedUntil, recordFailedLoginAttempt), requireAuth (lastSeenAt)</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -2284,7 +2268,7 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>users, sessions</t>
+          <t>users, sessions, login_attempts</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -2294,12 +2278,12 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>Prueba en navegador</t>
-        </is>
-      </c>
-      <c r="N25" s="9" t="inlineStr">
-        <is>
-          <t>Parcial (falta CA-03: registrar cada intento fallido)</t>
+          <t>Prueba en navegador; intentos registrados en login_attempts (27/10/2026)</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
     </row>
@@ -2336,42 +2320,42 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
+          <t>PoliticaDatosPage ( /politica-datos ), ProtectedRoute</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>POST /auth/policy/accept; 403 POLICY_REQUIRED en rutas de negocio</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>authService.acceptPolicy, middlewares/auth requireAuth / requireSession</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>users (policyAcceptance), sessions (policyAccepted)</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>auth.policy.test.ts</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="10" t="inlineStr">
-        <is>
-          <t>No implementado (falta el texto de la política)</t>
+          <t>docs/evidencias/politica-datos-primer-ingreso.jpg</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
     </row>
@@ -4027,17 +4011,17 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>authService.login · POST /auth/login (423) · LoginPage</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+          <t>authService.login (bloqueo y recordFailedLoginAttempt) · POST /auth/login (423) · LoginPage</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Bloqueo de 15 min tras 5 intentos; falta registrar cada intento (HU-022 CA-03).</t>
+          <t>Bloqueo de 15 min tras 5 intentos y registro de cada intento fallido (sin contraseña, 90 días).</t>
         </is>
       </c>
     </row>
@@ -4059,15 +4043,19 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>No implementado</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr"/>
+          <t>POST /auth/policy/accept · authService.acceptPolicy · requireAuth (403 POLICY_REQUIRED) · PoliticaDatosPage</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Política versión 1.0 (Ley 1581); se exige en el backend hasta aceptarla.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:F58"/>
